--- a/data/data_preparation/smartband/df_relation_matrix.xlsx
+++ b/data/data_preparation/smartband/df_relation_matrix.xlsx
@@ -1,38 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10313"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10611"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nachomondino/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C60D773-23D5-DD4E-9C35-7AB4EDC89E2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{378277AA-2120-9A4B-8B03-77F252178A1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
   <si>
     <t>customer_need</t>
   </si>
@@ -46,6 +34,12 @@
     <t>Material de la malla</t>
   </si>
   <si>
+    <t>Es resistente al agua</t>
+  </si>
+  <si>
+    <t>Tamaño de la pantalla</t>
+  </si>
+  <si>
     <t>Peso</t>
   </si>
   <si>
@@ -55,9 +49,6 @@
     <t>Duración de la batería</t>
   </si>
   <si>
-    <t>Tamaño de la pantalla</t>
-  </si>
-  <si>
     <t>Tipo de pantalla</t>
   </si>
   <si>
@@ -67,49 +58,22 @@
     <t>Con pantalla táctil</t>
   </si>
   <si>
-    <t>Con GPS</t>
-  </si>
-  <si>
-    <t>Profundidad máxima de resistencia al agua</t>
-  </si>
-  <si>
-    <t>Es resistente al agua</t>
-  </si>
-  <si>
-    <t>Funciones del smartwatch_Aplicacióndeportiva</t>
-  </si>
-  <si>
-    <t>Funciones del smartwatch_Calendario</t>
-  </si>
-  <si>
-    <t>Funciones del smartwatch_Consumodecalorías</t>
-  </si>
-  <si>
-    <t>Funciones del smartwatch_Cronómetro</t>
-  </si>
-  <si>
-    <t>Funciones del smartwatch_Cuentapasos</t>
+    <t>funciones</t>
+  </si>
+  <si>
+    <t>facil</t>
+  </si>
+  <si>
+    <t>conecta</t>
   </si>
   <si>
     <t>bateria</t>
   </si>
   <si>
-    <t>funciones</t>
-  </si>
-  <si>
-    <t>materiales</t>
-  </si>
-  <si>
-    <t>tamaño</t>
-  </si>
-  <si>
     <t>pantalla</t>
   </si>
   <si>
-    <t>agua</t>
-  </si>
-  <si>
-    <t>gps</t>
+    <t>diseño</t>
   </si>
 </sst>
 </file>
@@ -166,10 +130,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -473,69 +440,57 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S9"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:15" ht="48" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
-      </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -581,22 +536,10 @@
       <c r="O2">
         <v>0</v>
       </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -611,17 +554,17 @@
         <v>0</v>
       </c>
       <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
         <v>1</v>
       </c>
-      <c r="G3">
+      <c r="I3">
         <v>9</v>
       </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
       <c r="J3">
         <v>0</v>
       </c>
@@ -640,22 +583,10 @@
       <c r="O3">
         <v>0</v>
       </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -691,320 +622,201 @@
         <v>0</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N4">
         <v>0</v>
       </c>
       <c r="O4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
         <v>3</v>
       </c>
-      <c r="P4">
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
         <v>1</v>
       </c>
-      <c r="Q4">
+      <c r="L6">
         <v>1</v>
       </c>
-      <c r="R4">
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
         <v>1</v>
       </c>
-      <c r="S4">
-        <v>3</v>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>9</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>9</v>
-      </c>
-      <c r="J7">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
         <v>1</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>1</v>
-      </c>
-      <c r="N8">
-        <v>9</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>9</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/data_preparation/smartband/df_relation_matrix.xlsx
+++ b/data/data_preparation/smartband/df_relation_matrix.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,39 +446,39 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Capacidad de la batería</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Duración de la batería</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Tamaño de la pantalla</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo de pantalla</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Material de la malla</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Es resistente al agua</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Peso</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Capacidad de la batería</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Duración de la batería</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Tipo de pantalla</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Resolución máxima</t>
-        </is>
-      </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Con pantalla táctil</t>
@@ -486,20 +486,15 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Es resistente al agua</t>
+          <t>funciones</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>funciones</t>
+          <t>facil</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>facil</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>conecta</t>
         </is>
@@ -550,9 +545,6 @@
       <c r="N2" t="n">
         <v>0</v>
       </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -567,16 +559,16 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -597,9 +589,6 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -640,15 +629,12 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -692,12 +678,9 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -720,19 +703,19 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
@@ -744,9 +727,6 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -793,9 +773,6 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -812,39 +789,36 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
         <v>3</v>
       </c>
-      <c r="E8" t="n">
+      <c r="I8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" t="n">
         <v>1</v>
       </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/data_preparation/smartband/df_relation_matrix.xlsx
+++ b/data/data_preparation/smartband/df_relation_matrix.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,12 +491,7 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>facil</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>conecta</t>
+          <t>bluetooth</t>
         </is>
       </c>
     </row>
@@ -542,9 +537,6 @@
       <c r="M2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -588,9 +580,6 @@
       <c r="M3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -634,14 +623,11 @@
       <c r="M4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>pantalla</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -657,10 +643,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -672,22 +658,19 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>pantalla</t>
+          <t>diseño</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -703,37 +686,34 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>conecta</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -770,56 +750,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>diseño</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I8" t="n">
-        <v>3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
